--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0224.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0224.xlsx
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Làm Mới ({0}/{1})</t>
+          <t>Làm mới ({0}/{1})</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Saved&lt;/color&gt;</t>
+          <t>&lt;color=Highlight&gt;Đã lưu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>&lt;color=#e4e4e4ff&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>&lt;color=#e4e4e4ff&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Khi đánh bại Tacet Discord này, nó sẽ triệu hồi &lt;color=#fde7a1ff&gt;one&lt;/color&gt; Chop Chop: Headless và &lt;color=#fde7a1ff&gt;three&lt;/color&gt; Tick Tack.</t>
+          <t>Khi đánh bại Tacet Discord này, nó sẽ triệu hồi &lt;color=#fde7a1ff&gt;một&lt;/color&gt; Chop Chop: Headless và &lt;color=#fde7a1ff&gt;ba&lt;/color&gt; Tick Tack.</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Tactic Set tập trung vào kiểm soát hỏa lực bằng cách tăng Attack Speed và hiệu ứng Control.</t>
+          <t>Bộ Chiến Thuật tập trung vào kiểm soát hỏa lực bằng cách tăng Tốc Độ Tấn Công và hiệu ứng Điều Khiển.</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Tactic Set tối ưu hóa hiệu suất thu thập tài nguyên và chuyển hóa lượng tài nguyên dư thừa thành sức mạnh tấn công.</t>
+          <t>Bộ Chiến Thuật tối ưu hóa hiệu suất thu thập tài nguyên và chuyển hóa lượng tài nguyên dư thừa thành sức mạnh tấn công.</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Giữ vững đến Hồi 20 và kích hoạt bất kỳ Chiến Thuật Vàng nào từ Bộ Chiến Thuật Cộng Hưởng Tiếng Vang trong "Bài Kiểm Tra Phòng Ngự Toàn Diện".</t>
+          <t>Giữ vững đến Hồi 20 và kích hoạt bất kỳ Chiến Thuật Vàng nào từ Bộ Chiến Thuật Cộng Hưởng Echo trong "Bài Kiểm Tra Phòng Ngự Toàn Diện".</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Tactic Set tập trung vào kiểm soát hỏa lực bằng cách tăng Attack Speed và hiệu ứng Control.</t>
+          <t>Bộ Chiến Thuật tập trung vào kiểm soát hỏa lực bằng cách tăng Tốc Độ Tấn Công và hiệu ứng Điều Khiển.</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Tactic Set tối ưu hóa hiệu suất thu thập tài nguyên và chuyển hóa lượng tài nguyên dư thừa thành sức mạnh tấn công.</t>
+          <t>Bộ Chiến Thuật tối ưu hóa hiệu suất thu thập tài nguyên và chuyển hóa lượng tài nguyên dư thừa thành sức mạnh tấn công.</t>
         </is>
       </c>
     </row>
@@ -16645,7 +16645,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Hiện tại, Chiến Thuật hiếm cấp &lt;color=Rare3&gt;Blue&lt;/color&gt; hoặc thấp hơn có thể xuất hiện.</t>
+          <t>Hiện tại, Chiến Thuật hiếm cấp &lt;color=Rare3&gt;Xanh lam&lt;/color&gt; hoặc thấp hơn có thể xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Hiện tại, Chiến Thuật hiếm cấp &lt;color=Rare4&gt;Purple&lt;/color&gt; hoặc thấp hơn có thể xuất hiện.</t>
+          <t>Hiện tại, Chiến Thuật hiếm cấp &lt;color=Rare4&gt;Tím&lt;/color&gt; hoặc thấp hơn có thể xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Hiện tại, Chiến Thuật hiếm cấp &lt;color=Rare5&gt;Gold&lt;/color&gt; hoặc thấp hơn có thể xuất hiện.</t>
+          <t>Hiện tại, Chiến Thuật hiếm cấp &lt;color=Rare5&gt;Vàng&lt;/color&gt; hoặc thấp hơn có thể xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16970,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Khi một Tổ Tacet trên chiến trường bắt đầu &lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt;, có {0}% khả năng tạo ra một bản sao của nó trên một ô trống.</t>
+          <t>Khi một Tổ Tacet trên chiến trường bắt đầu &lt;te href=851008&gt;&lt;color=#c79f49&gt;Hấp Thu&lt;/color&gt;&lt;/te&gt;, có {0}% khả năng tạo ra một bản sao của nó trên một ô trống.</t>
         </is>
       </c>
     </row>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>&lt;te href=851008&gt;&lt;color=#c79f49&gt;Integration&lt;/color&gt;&lt;/te&gt; đầu tiên trong ngày cần ít hơn &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echo}.</t>
+          <t>&lt;te href=851008&gt;&lt;color=#c79f49&gt;Hợp Nhất&lt;/color&gt;&lt;/te&gt; đầu tiên trong ngày cần ít hơn &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Echo P=Echo}.</t>
         </is>
       </c>
     </row>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>&lt;te href=851045&gt;&lt;color=#c79f49&gt;Basic Form&lt;/color&gt;&lt;/te&gt;</t>
+          <t>&lt;te href=851045&gt;&lt;color=#c79f49&gt;Hình Thái Cơ Bản&lt;/color&gt;&lt;/te&gt;</t>
         </is>
       </c>
     </row>
@@ -19116,7 +19116,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>&lt;color=#d5b55e&gt;Current&lt;/color&gt;</t>
+          <t>&lt;color=#d5b55e&gt;Hiện tại&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19181,7 +19181,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>&lt;color=#5ed5af&gt;Preview&lt;/color&gt;</t>
+          <t>&lt;color=#5ed5af&gt;Xem trước&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>&lt;color=#84c6f5&gt;Preview&lt;/color&gt;</t>
+          <t>&lt;color=#84c6f5&gt;Xem trước&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19441,7 +19441,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>&lt;color=#c25757&gt;Consider switching to a weapon of higher quality&lt;/color&gt;</t>
+          <t>&lt;color=#c25757&gt;Nên cân nhắc đổi sang vũ khí chất lượng cao hơn&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -19506,7 +19506,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>&lt;color=#36cd33&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -19571,7 +19571,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>&lt;\color=#ffd12f&gt;{0}&lt;/color&gt;</t>
+          <t>{0}</t>
         </is>
       </c>
     </row>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>To the Heroes...</t>
+          <t>Tới Những Người Anh Hùng...</t>
         </is>
       </c>
     </row>
@@ -30558,7 +30558,7 @@
       <c r="M463" t="inlineStr">
         <is>
           <t>Phóng &lt;color=#be6245&gt;&lt;te href=800022&gt;Blazing Stars&lt;/te&gt;&lt;/color&gt; từ trên trời.
-Loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Bullet Weapon&lt;/te&gt;]&lt;/color&gt;</t>
+Loại: &lt;color=#c49e55&gt;[&lt;te href=800026&gt;Vũ khí đạn đạo&lt;/te&gt;]&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -31338,7 +31338,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Cấp Độ Cộng Hưởng Giả +{0}</t>
+          <t>Cấp Độ Resonator +{0}</t>
         </is>
       </c>
     </row>
@@ -31468,7 +31468,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=Touch} bất cứ đâu để đóng</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Tap} bất cứ đâu để đóng</t>
         </is>
       </c>
     </row>
